--- a/data/trans_bre/P2A_senso_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,05</t>
+          <t>-2,37; 1,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,25</t>
+          <t>-3,17; 3,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,32</t>
+          <t>-0,52; 3,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,37</t>
+          <t>-0,99; 2,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,55; 197,29</t>
+          <t>-63,09; 199,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,25; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-76,91; —</t>
+          <t>-70,26; —</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,01</t>
+          <t>-2,65; 0,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,01</t>
+          <t>-1,26; 2,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,86</t>
+          <t>-0,78; 0,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,17</t>
+          <t>-2,12; 3,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,75; 94,46</t>
+          <t>-77,17; 76,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,75; 283,69</t>
+          <t>-58,06; 373,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 85,4</t>
+          <t>-31,68; 95,68</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,56</t>
+          <t>-1,1; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,92</t>
+          <t>-3,6; 0,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,07</t>
+          <t>-1,71; 1,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,6</t>
+          <t>-3,1; 0,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 162,72</t>
+          <t>-93,12; 152,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,31; 54,46</t>
+          <t>-80,02; 75,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,56</t>
+          <t>-3,25; 0,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,9</t>
+          <t>0,53; 4,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,3</t>
+          <t>-0,6; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,35</t>
+          <t>-3,76; 1,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,61; 67,23</t>
+          <t>-88,68; 61,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 1369,03</t>
+          <t>-12,58; 2031,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,05; —</t>
+          <t>-64,34; 1411,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-83,71; 160,42</t>
+          <t>-85,4; 149,91</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,06</t>
+          <t>-1,38; 6,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 3,95</t>
+          <t>-6,46; 3,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,89</t>
+          <t>-0,34; 2,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 336,5</t>
+          <t>-40,59; 477,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,86; 90,1</t>
+          <t>-64,94; 90,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,3; —</t>
+          <t>-53,1; —</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,69</t>
+          <t>-1,26; 0,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,52</t>
+          <t>-0,76; 2,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,04</t>
+          <t>-3,99; 1,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,98</t>
+          <t>-0,85; 4,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-89,45; 138,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 240,48</t>
+          <t>-26,97; 314,08</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,68</t>
+          <t>-1,43; 1,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,25</t>
+          <t>-0,37; 2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,1</t>
+          <t>-1,48; 1,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 56,96</t>
+          <t>1,35; 61,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-54,99; 210,5</t>
+          <t>-58,97; 155,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-30,27; 403,4</t>
+          <t>-31,27; 492,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 160,04</t>
+          <t>-71,18; 170,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,39; 2759,59</t>
+          <t>35,7; 2487,95</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,3</t>
+          <t>-0,27; 2,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,59</t>
+          <t>-0,45; 1,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,71</t>
+          <t>-1,18; 0,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,89</t>
+          <t>-0,26; 0,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 381,52</t>
+          <t>-24,66; 388,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,16; 370,09</t>
+          <t>-43,63; 394,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 196,03</t>
+          <t>-76,62; 207,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,03; 1127,73</t>
+          <t>-62,03; 1720,56</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,71</t>
+          <t>-0,51; 0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,13</t>
+          <t>-0,17; 1,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,57</t>
+          <t>-0,49; 0,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 23,16</t>
+          <t>0,47; 23,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 56,33</t>
+          <t>-28,66; 58,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 80,11</t>
+          <t>-8,54; 90,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 73,93</t>
+          <t>-38,88; 69,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,06; 1225,76</t>
+          <t>19,72; 1180,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>109,63%</t>
+          <t>165,26%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,9</t>
+          <t>-2,19; 2,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,5</t>
+          <t>-2,86; 3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,24</t>
+          <t>-0,48; 3,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,55</t>
+          <t>-0,44; 2,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,09; 199,33</t>
+          <t>-59,05; 197,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,21; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,26; —</t>
+          <t>-61,01; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,89</t>
+          <t>-2,65; 0,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,07</t>
+          <t>-1,16; 2,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,85</t>
+          <t>-0,77; 0,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 3,3</t>
+          <t>-1,55; 3,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,17; 76,0</t>
+          <t>-75,58; 77,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 373,18</t>
+          <t>-59,51; 350,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 95,68</t>
+          <t>-26,47; 86,57</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,47%</t>
+          <t>-40,65%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,55</t>
+          <t>-1,39; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,79</t>
+          <t>-3,36; 0,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,07</t>
+          <t>-1,48; 1,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,66</t>
+          <t>-2,99; 0,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-93,12; 152,71</t>
+          <t>-100,0; 161,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 75,87</t>
+          <t>-79,26; 60,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,9%</t>
+          <t>-16,7%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,61</t>
+          <t>-3,4; 0,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,87</t>
+          <t>0,38; 4,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,63</t>
+          <t>-0,57; 3,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,29</t>
+          <t>-3,18; 1,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,68; 61,9</t>
+          <t>-86,32; 59,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 2031,64</t>
+          <t>-18,83; 1341,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,34; 1411,63</t>
+          <t>-70,92; 1158,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,4; 149,91</t>
+          <t>-79,96; 260,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>208,28%</t>
+          <t>306,69%</t>
         </is>
       </c>
     </row>
@@ -1060,32 +1060,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,24</t>
+          <t>-1,35; 6,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 3,74</t>
+          <t>-6,29; 3,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>-2,93; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,99</t>
+          <t>0,33; 3,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 477,93</t>
+          <t>-40,6; 360,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-64,94; 90,81</t>
+          <t>-68,23; 92,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,1; —</t>
+          <t>-42,26; —</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,69</t>
+          <t>-1,23; 0,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,24</t>
+          <t>-0,77; 2,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,03</t>
+          <t>-3,94; 1,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 4,2</t>
+          <t>-1,49; 3,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,62; 155,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 314,08</t>
+          <t>-36,98; 205,94</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>711,75%</t>
+          <t>51,88%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,44</t>
+          <t>-1,4; 1,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,34</t>
+          <t>-0,39; 2,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,2</t>
+          <t>-1,7; 1,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 61,34</t>
+          <t>-0,06; 4,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-58,97; 155,71</t>
+          <t>-58,53; 152,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,27; 492,77</t>
+          <t>-37,96; 465,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 170,17</t>
+          <t>-73,1; 178,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,7; 2487,95</t>
+          <t>-4,36; 146,98</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,37</t>
+          <t>-0,27; 2,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,66</t>
+          <t>-0,58; 1,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,77</t>
+          <t>-1,14; 0,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,91</t>
+          <t>-0,99; 0,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 388,62</t>
+          <t>-32,9; 406,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,63; 394,38</t>
+          <t>-44,46; 353,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,62; 207,46</t>
+          <t>-81,35; 206,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,03; 1720,56</t>
+          <t>-77,27; 310,27</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,06</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>273,33%</t>
+          <t>29,64%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,74</t>
+          <t>-0,48; 0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,2</t>
+          <t>-0,2; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,54</t>
+          <t>-0,43; 0,56</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 23,23</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,66; 58,47</t>
+          <t>-26,27; 57,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 90,33</t>
+          <t>-11,01; 86,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-38,88; 69,91</t>
+          <t>-34,58; 78,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19,72; 1180,41</t>
+          <t>-0,19; 70,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_senso_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_senso_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
